--- a/output/2026-09-16_00_Croazia_Brodsko-posavska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-16_00_Croazia_Brodsko-posavska_ATEX_Equipment-Services.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Croazia per Robuschi, Elmo Rietschle, Wittig, NASH; vendita e noleggio macchinari industriali/edili. Contatti confermati da fonte indipendente (kompass.com).</t>
+          <t>Distributore ufficiale Croazia per Robuschi, Elmo Rietschle, Wittig, NASH; vendita e noleggio macchinari industriali/edili. Contatti confermati da fonte indipendente (kompass.com). [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -540,7 +540,6 @@
           <t>+385 35 446 269 / +385 98 504 257</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Produzione/vendita motori elettrici, generatori, trasformatori; servizi di collaudo/certificazione. Nessuna fonte pubblica conferma esplicitamente offerta ATEX/Ex specifica: verifica diretta consigliata prima di contatto commerciale.</t>
